--- a/output/pdf_financials_xlsx/CSL.H.xlsx
+++ b/output/pdf_financials_xlsx/CSL.H.xlsx
@@ -5580,49 +5580,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.08744300000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.260669</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.7213619999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.009668</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.009668</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.009668</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.83377</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.388521</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.530171</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.607064</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.612965</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.703965</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.703965</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.703965</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.703965</v>
       </c>
     </row>
     <row r="93">
@@ -8961,7 +8961,11 @@
           <t>Share‐based payment reserve 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10096,7 +10100,11 @@
           <t>Share‐based payment reserve 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12756,7 +12764,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15897,7 +15909,11 @@
           <t>Share‐based payment reserve 9</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.08744300000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/CSL.H.xlsx
+++ b/output/pdf_financials_xlsx/CSL.H.xlsx
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011645</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.025761</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02673</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007148</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002163</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.016929</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.009103999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.009102000000000001</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001157</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001077</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000356</v>
       </c>
     </row>
     <row r="13">
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.411831</v>
+        <v>-0.423476</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.204288</v>
+        <v>-1.230049</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.755053</v>
+        <v>-0.781783</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.292166</v>
+        <v>-2.299314</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2047,16 +2047,16 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.633253</v>
+        <v>-1.635416</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.051207</v>
+        <v>-1.068136</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.000434</v>
+        <v>-4.009538</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.176792</v>
+        <v>-6.185894</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.223989</v>
+        <v>-1.225146</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.076544</v>
+        <v>-0.077621</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.411831</v>
+        <v>-0.423476</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.204288</v>
+        <v>-1.230049</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.755053</v>
+        <v>-0.781783</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.292166</v>
+        <v>-2.299314</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2169,16 +2169,16 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.633253</v>
+        <v>-1.635416</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.051207</v>
+        <v>-1.068136</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.000434</v>
+        <v>-4.009538</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.176792</v>
+        <v>-6.185894</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.223989</v>
+        <v>-1.225146</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.076544</v>
+        <v>-0.077621</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2457,34 +2457,34 @@
         <v>0.164535</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.026284</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.120393</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.404586</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.5911459999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.217726</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.189961</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.059811</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.058978</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.008434000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.038096</v>
       </c>
     </row>
     <row r="35">
@@ -2561,34 +2561,34 @@
         <v>0.164535</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.026284</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.120393</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.404586</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.5911459999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.217726</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.189961</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.059811</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.058978</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.008434000000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.038096</v>
       </c>
     </row>
     <row r="37">
@@ -3185,19 +3185,19 @@
         <v>0.025239</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.027584</v>
+        <v>0.0013</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.204142</v>
+        <v>0.083749</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.479337</v>
+        <v>0.074751</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.860994</v>
+        <v>3.269848</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.237251</v>
+        <v>0.019525</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -3206,13 +3206,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.766811</v>
+        <v>0.707833</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.716109</v>
+        <v>0.7076750000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.880167</v>
+        <v>0.842071</v>
       </c>
     </row>
     <row r="49">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27243,7 +27243,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -28505,7 +28505,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -29055,7 +29055,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -33147,7 +33147,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">

--- a/output/pdf_financials_xlsx/CSL.H.xlsx
+++ b/output/pdf_financials_xlsx/CSL.H.xlsx
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.091935</v>
+        <v>0.186483</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.21732</v>
+        <v>0.440997</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.137218</v>
+        <v>0.304718</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.112675</v>
+        <v>0.318513</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.091935</v>
+        <v>0.186483</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.21732</v>
+        <v>0.440997</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.137218</v>
+        <v>0.304718</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.112675</v>
+        <v>0.318513</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1342,10 +1342,8 @@
       <c r="O16" s="3" t="n">
         <v>-0.076544</v>
       </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P16" s="3" t="n">
+        <v>0.32177</v>
       </c>
     </row>
     <row r="17">
@@ -1628,10 +1626,8 @@
       <c r="O20" s="3" t="n">
         <v>-0.076544</v>
       </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P20" s="3" t="n">
+        <v>0.32177</v>
       </c>
     </row>
     <row r="21">
@@ -1810,10 +1806,8 @@
       <c r="O23" s="3" t="n">
         <v>-0.076544</v>
       </c>
-      <c r="P23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P23" s="3" t="n">
+        <v>0.32177</v>
       </c>
     </row>
     <row r="24">
@@ -2074,10 +2068,8 @@
       <c r="O27" s="3" t="n">
         <v>-0.077621</v>
       </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P27" s="3" t="n">
+        <v>0.321414</v>
       </c>
     </row>
     <row r="28">
@@ -2196,10 +2188,8 @@
       <c r="O29" s="3" t="n">
         <v>-0.077621</v>
       </c>
-      <c r="P29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P29" s="3" t="n">
+        <v>0.321414</v>
       </c>
     </row>
     <row r="30">
@@ -2340,10 +2330,8 @@
       <c r="O31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4220,10 +4208,10 @@
         <v>0.379289</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -5948,10 +5936,8 @@
       <c r="O99" s="3" t="n">
         <v>-0.076544</v>
       </c>
-      <c r="P99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P99" s="3" t="n">
+        <v>0.32177</v>
       </c>
     </row>
     <row r="100">
@@ -17078,7 +17064,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -29917,7 +29907,11 @@
           <t>Management and director fees 8</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
